--- a/docs/Mapping_casi_uso/matrimoni/Matr_019.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_019.xlsx
@@ -659,7 +659,7 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -668,7 +668,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -677,7 +677,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Madre Sposa</t>
@@ -686,7 +686,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Tutore Sposo</t>
@@ -695,13 +695,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposo</t>
@@ -710,7 +710,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Tutore Sposa</t>
@@ -719,13 +719,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposa</t>
@@ -734,7 +734,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Estremi Certificazione</t>
@@ -857,13 +857,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -967,7 +967,7 @@
     <col min="4" max="4" width="59.5078125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="32.48828125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="114.08984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8335,10 +8335,10 @@
         <v>213</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>214</v>
@@ -8979,10 +8979,10 @@
         <v>216</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>217</v>
@@ -9623,10 +9623,10 @@
         <v>219</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D377" s="2" t="s">
         <v>220</v>
@@ -10267,10 +10267,10 @@
         <v>222</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D405" s="2" t="s">
         <v>223</v>
@@ -10911,10 +10911,10 @@
         <v>225</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D433" s="2" t="s">
         <v>226</v>
@@ -11555,10 +11555,10 @@
         <v>228</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D461" s="2" t="s">
         <v>226</v>
@@ -12360,10 +12360,10 @@
         <v>233</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D496" s="2" t="s">
         <v>234</v>
@@ -13004,10 +13004,10 @@
         <v>236</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D524" s="2" t="s">
         <v>234</v>
@@ -14419,7 +14419,7 @@
         <v>282</v>
       </c>
       <c r="F585" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G585" s="2" t="s">
         <v>47</v>
